--- a/src/tests/audio/ear_test_matrix.xlsx
+++ b/src/tests/audio/ear_test_matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manasseh/Projects/hit400/sna-data-pipeline/src/tests/audio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{332AB2AC-B8E2-584A-B2D0-C0EA01EB1800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AAF9F408-C47E-1242-BE36-475619FB5542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{B639A930-7760-2846-BEB6-BA97A097B2A6}"/>
+    <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" xr2:uid="{B639A930-7760-2846-BEB6-BA97A097B2A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ear_test_matrix" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
-  <si>
-    <t>rank</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="105">
   <si>
     <t>speaker_id</t>
   </si>
@@ -37,9 +34,6 @@
     <t>naturalness_1_to_5</t>
   </si>
   <si>
-    <t>quality_consistency_yes_mixed_no</t>
-  </si>
-  <si>
     <t>identity_consistent_yes_no</t>
   </si>
   <si>
@@ -284,6 +278,63 @@
   </si>
   <si>
     <t>39_FjWt9cvjUvSd8Gn5y0FTqctULdg2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">speaker makes too many errors and audio quailty is highly inconsistent and at times inaudible, workable after noise reduction and volume normalization </t>
+  </si>
+  <si>
+    <t>quality_consistency/5</t>
+  </si>
+  <si>
+    <t>speaker has good energy, but its clear its not their conversational tone, its as if he is reading a news report, but overall prestine quality very good</t>
+  </si>
+  <si>
+    <t>speaker is good, but some clips have reverb like she is in a large room , need snormalization</t>
+  </si>
+  <si>
+    <t>contaiminated labled as female speaker but of the samples we have 15 male / 5 female, male generally has good quality female quality is mixed</t>
+  </si>
+  <si>
+    <t>speaker is good, some clips have lower quality a bit muffled but overall permissable</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>contaminated mixed speakers both male and female, labled as female but we have about 5 male clips</t>
+  </si>
+  <si>
+    <t>inconsistent quality, low volume cilps, mixed high and low quality needs normalizzaiton otherwise audible</t>
+  </si>
+  <si>
+    <t>needs volume normalization, mic pops in most clips at beginning of recording 'mic on pop'</t>
+  </si>
+  <si>
+    <t>neds volume normalization</t>
+  </si>
+  <si>
+    <t>needs heavy volume normalization</t>
+  </si>
+  <si>
+    <t>mid-low quality</t>
+  </si>
+  <si>
+    <t>high - prestine</t>
+  </si>
+  <si>
+    <t>mid-high</t>
+  </si>
+  <si>
+    <t>mid</t>
   </si>
 </sst>
 </file>
@@ -1144,246 +1195,485 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544300B8-6A37-7F4D-9841-E8B6C996F47D}">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="9.5" customWidth="1"/>
+    <col min="3" max="3" width="3.33203125" customWidth="1"/>
+    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D7">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" t="s">
+        <v>97</v>
+      </c>
+      <c r="K8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D9">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D10">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" t="s">
+        <v>99</v>
+      </c>
+      <c r="K10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D12">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" t="s">
+        <v>100</v>
+      </c>
+      <c r="K12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D13">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D16">
         <v>20</v>
@@ -1394,10 +1684,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17">
         <v>20</v>
@@ -1408,10 +1698,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D18">
         <v>20</v>
@@ -1422,10 +1712,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D19">
         <v>20</v>
@@ -1436,10 +1726,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D20">
         <v>20</v>
@@ -1450,10 +1740,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1464,10 +1754,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D22">
         <v>20</v>
@@ -1478,10 +1768,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D23">
         <v>20</v>
@@ -1492,10 +1782,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D24">
         <v>20</v>
@@ -1506,10 +1796,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D25">
         <v>20</v>
@@ -1520,10 +1810,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="D26">
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -1531,10 +1824,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D27">
         <v>20</v>
@@ -1545,10 +1838,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D28">
         <v>20</v>
@@ -1559,10 +1852,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D29">
         <v>20</v>
@@ -1573,10 +1866,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D30">
         <v>20</v>
@@ -1587,10 +1880,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D31">
         <v>20</v>
@@ -1601,10 +1894,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D32">
         <v>20</v>
@@ -1615,10 +1908,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D33">
         <v>20</v>
@@ -1629,10 +1922,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D34">
         <v>20</v>
@@ -1643,10 +1936,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D35">
         <v>20</v>
@@ -1657,10 +1950,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D36">
         <v>20</v>
@@ -1671,10 +1964,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D37">
         <v>20</v>
@@ -1685,10 +1978,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D38">
         <v>20</v>
@@ -1699,10 +1992,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D39">
         <v>20</v>
@@ -1713,10 +2006,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D40">
         <v>20</v>
